--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>19.47905682339649</v>
+        <v>3.16534673380193</v>
       </c>
       <c r="D2" t="n">
-        <v>19.13701358333869</v>
+        <v>3.109764707292536</v>
       </c>
       <c r="E2" t="n">
-        <v>19.14767349696791</v>
+        <v>3.111496943257285</v>
       </c>
       <c r="F2" t="n">
-        <v>19.09507323690741</v>
+        <v>3.102949400997454</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.69616141643742</v>
+        <v>3.363126230171082</v>
       </c>
       <c r="D3" t="n">
-        <v>14.25286085885888</v>
+        <v>2.316089889564568</v>
       </c>
       <c r="E3" t="n">
-        <v>19.14767349696791</v>
+        <v>3.111496943257285</v>
       </c>
       <c r="F3" t="n">
-        <v>19.09507323690741</v>
+        <v>3.102949400997454</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.82553693807358</v>
+        <v>6.471649752436957</v>
       </c>
       <c r="D4" t="n">
-        <v>39.96652740614863</v>
+        <v>6.494560703499152</v>
       </c>
       <c r="E4" t="n">
-        <v>19.14767349696791</v>
+        <v>3.111496943257285</v>
       </c>
       <c r="F4" t="n">
-        <v>19.09507323690741</v>
+        <v>3.102949400997454</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.74638142831738</v>
+        <v>2.396286982101575</v>
       </c>
       <c r="D5" t="n">
-        <v>15.05738131303438</v>
+        <v>2.446824463368086</v>
       </c>
       <c r="E5" t="n">
-        <v>19.14767349696791</v>
+        <v>3.111496943257285</v>
       </c>
       <c r="F5" t="n">
-        <v>19.09507323690741</v>
+        <v>3.102949400997454</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.82021970119987</v>
+        <v>8.420785701444981</v>
       </c>
       <c r="D6" t="n">
-        <v>52.31011969229492</v>
+        <v>8.500394449997925</v>
       </c>
       <c r="E6" t="n">
-        <v>19.14767349696791</v>
+        <v>3.111496943257285</v>
       </c>
       <c r="F6" t="n">
-        <v>19.09507323690741</v>
+        <v>3.102949400997454</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.2117528243825</v>
+        <v>1.984409833962157</v>
       </c>
       <c r="D7" t="n">
-        <v>13.92795621039868</v>
+        <v>2.263292884189786</v>
       </c>
       <c r="E7" t="n">
-        <v>19.14767349696791</v>
+        <v>3.111496943257285</v>
       </c>
       <c r="F7" t="n">
-        <v>19.09507323690741</v>
+        <v>3.102949400997454</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.84717643712496</v>
+        <v>5.987666171032807</v>
       </c>
       <c r="D8" t="n">
-        <v>35.34313973782304</v>
+        <v>5.743260207396244</v>
       </c>
       <c r="E8" t="n">
-        <v>19.14767349696791</v>
+        <v>3.111496943257285</v>
       </c>
       <c r="F8" t="n">
-        <v>19.09507323690741</v>
+        <v>3.102949400997454</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.33089252758811</v>
+        <v>7.528770035733069</v>
       </c>
       <c r="D9" t="n">
-        <v>44.98904356295249</v>
+        <v>7.310719578979779</v>
       </c>
       <c r="E9" t="n">
-        <v>19.14767349696791</v>
+        <v>3.111496943257285</v>
       </c>
       <c r="F9" t="n">
-        <v>19.09507323690741</v>
+        <v>3.102949400997454</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>68.8623366958459</v>
+        <v>11.19012971307496</v>
       </c>
       <c r="D10" t="n">
-        <v>67.0273456738621</v>
+        <v>10.89194367200259</v>
       </c>
       <c r="E10" t="n">
-        <v>19.14767349696791</v>
+        <v>3.111496943257285</v>
       </c>
       <c r="F10" t="n">
-        <v>19.09507323690741</v>
+        <v>3.102949400997454</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>62.59493166415511</v>
+        <v>10.17167639542521</v>
       </c>
       <c r="D11" t="n">
-        <v>61.26942687239993</v>
+        <v>9.956281866764987</v>
       </c>
       <c r="E11" t="n">
-        <v>19.14767349696791</v>
+        <v>3.111496943257285</v>
       </c>
       <c r="F11" t="n">
-        <v>19.09507323690741</v>
+        <v>3.102949400997454</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
